--- a/data/trans_dic/P2C_R-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P2C_R-Provincia-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -526,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Entrevistados que realiza cuidados a personas del hogar que lo requieren</t>
+          <t>Entrevistados que realiza cuidados a personas del hogar que lo requieren (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -638,7 +639,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Almeria</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -716,69 +717,69 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>72,86; 90,41</t>
+          <t>72,95; 90,81</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>86,39; 100,0</t>
+          <t>86,93; 100,0</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>59,39; 81,54</t>
+          <t>59,07; 80,13</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>8,26; 39,84</t>
+          <t>7,76; 43,02</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>74,65; 91,35</t>
+          <t>73,83; 91,61</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>91,14; 100,0</t>
+          <t>90,01; 100,0</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>63,32; 83,73</t>
+          <t>63,84; 83,92</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>3,98; 15,01</t>
+          <t>4,0; 14,83</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>77,2; 89,75</t>
+          <t>77,26; 88,85</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>92,83; 99,23</t>
+          <t>92,85; 99,19</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>64,11; 79,19</t>
+          <t>65,14; 79,16</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>7,32; 23,62</t>
+          <t>7,4; 25,86</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Cadiz</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -856,69 +857,69 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>45,81; 64,68</t>
+          <t>45,16; 64,64</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>78,82; 93,05</t>
+          <t>77,5; 92,88</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>56,15; 74,69</t>
+          <t>55,74; 74,51</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6,86; 21,09</t>
+          <t>6,24; 21,06</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>39,25; 59,21</t>
+          <t>39,36; 59,1</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>81,6; 94,74</t>
+          <t>83,12; 94,8</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>59,28; 75,69</t>
+          <t>59,7; 76,52</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>14,04; 27,45</t>
+          <t>13,66; 27,82</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>44,97; 59,9</t>
+          <t>45,43; 59,27</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>82,97; 92,7</t>
+          <t>82,93; 92,85</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>60,43; 72,62</t>
+          <t>60,98; 73,05</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>11,18; 22,3</t>
+          <t>11,61; 22,13</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Cordoba</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -996,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>60,95; 79,22</t>
+          <t>60,8; 79,53</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>83,24; 97,28</t>
+          <t>82,82; 97,11</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>52,89; 74,86</t>
+          <t>52,65; 74,04</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>10,28; 24,65</t>
+          <t>9,98; 25,61</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>67,6; 83,86</t>
+          <t>68,22; 83,61</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>80,67; 94,35</t>
+          <t>80,69; 94,42</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>49,56; 69,56</t>
+          <t>49,65; 69,22</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>8,43; 22,23</t>
+          <t>9,3; 21,5</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>66,65; 79,63</t>
+          <t>67,38; 79,89</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>84,52; 94,43</t>
+          <t>84,62; 94,16</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>54,2; 68,59</t>
+          <t>54,15; 68,45</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>10,72; 20,71</t>
+          <t>11,47; 21,34</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>70,94; 87,36</t>
+          <t>71,46; 87,31</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>75,57; 92,49</t>
+          <t>75,48; 92,88</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>42,9; 67,27</t>
+          <t>43,42; 67,78</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>21,04; 40,4</t>
+          <t>20,59; 39,76</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>71,14; 86,75</t>
+          <t>72,51; 87,1</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>67,77; 88,29</t>
+          <t>69,38; 87,94</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>67,17; 87,26</t>
+          <t>66,43; 87,05</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>32,02; 69,22</t>
+          <t>31,2; 68,06</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>73,98; 84,96</t>
+          <t>74,14; 84,8</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>75,98; 88,6</t>
+          <t>75,59; 88,37</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>59,0; 74,86</t>
+          <t>57,95; 74,57</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>29,62; 53,07</t>
+          <t>29,1; 51,8</t>
         </is>
       </c>
     </row>
@@ -1276,69 +1277,69 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>48,75; 92,62</t>
+          <t>48,45; 92,59</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>71,53; 100,0</t>
+          <t>71,6; 100,0</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>83,09; 98,23</t>
+          <t>80,07; 98,22</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>15,02; 37,3</t>
+          <t>15,3; 36,59</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>24,53; 74,88</t>
+          <t>24,17; 73,54</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>68,03; 93,86</t>
+          <t>66,72; 92,01</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>89,14; 100,0</t>
+          <t>89,31; 100,0</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>23,32; 47,94</t>
+          <t>21,62; 46,85</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>42,28; 79,39</t>
+          <t>43,68; 76,46</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>74,94; 93,54</t>
+          <t>75,52; 93,39</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>89,33; 98,2</t>
+          <t>88,41; 98,12</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>21,7; 37,63</t>
+          <t>21,83; 37,79</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>Jaen</t>
+          <t>Jaén</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1416,69 +1417,69 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>55,96; 77,46</t>
+          <t>56,19; 78,21</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>80,78; 96,64</t>
+          <t>81,82; 96,68</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>46,22; 78,52</t>
+          <t>45,58; 76,0</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>21,83; 42,34</t>
+          <t>22,08; 42,4</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>56,12; 77,92</t>
+          <t>56,73; 77,27</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>78,57; 93,94</t>
+          <t>76,83; 93,36</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>59,01; 86,45</t>
+          <t>59,02; 85,5</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>31,0; 51,47</t>
+          <t>32,02; 52,89</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>60,14; 75,73</t>
+          <t>60,32; 75,14</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>82,97; 93,78</t>
+          <t>83,46; 93,68</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>59,53; 78,65</t>
+          <t>58,2; 78,2</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>29,42; 43,79</t>
+          <t>30,02; 44,92</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Malaga</t>
+          <t>Málaga</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -1556,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>72,57; 85,35</t>
+          <t>71,47; 84,18</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>88,29; 95,92</t>
+          <t>87,78; 95,91</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>56,66; 71,71</t>
+          <t>57,02; 71,1</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3,45; 10,25</t>
+          <t>3,54; 10,97</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>60,88; 75,22</t>
+          <t>60,77; 75,67</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>83,14; 93,0</t>
+          <t>83,89; 92,92</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>59,3; 73,47</t>
+          <t>59,85; 73,3</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>3,37; 11,51</t>
+          <t>3,2; 11,3</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>68,4; 78,26</t>
+          <t>69,24; 78,52</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>87,39; 93,56</t>
+          <t>87,18; 93,5</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>59,78; 70,56</t>
+          <t>60,1; 70,25</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>4,0; 9,37</t>
+          <t>4,0; 9,29</t>
         </is>
       </c>
     </row>
@@ -1696,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>44,26; 61,62</t>
+          <t>45,19; 62,37</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>82,06; 91,95</t>
+          <t>81,85; 91,7</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>88,47; 95,92</t>
+          <t>88,43; 95,79</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>73,05; 85,87</t>
+          <t>73,9; 86,36</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>54,86; 69,87</t>
+          <t>54,31; 70,63</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>80,93; 91,1</t>
+          <t>81,45; 91,24</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>84,24; 93,04</t>
+          <t>84,45; 93,31</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>74,74; 85,78</t>
+          <t>73,99; 85,82</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>52,01; 63,44</t>
+          <t>51,76; 63,21</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>83,38; 90,28</t>
+          <t>83,43; 90,25</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>88,16; 93,61</t>
+          <t>88,2; 93,68</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>75,83; 84,82</t>
+          <t>76,25; 84,53</t>
         </is>
       </c>
     </row>
@@ -1836,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>66,16; 72,69</t>
+          <t>66,23; 72,84</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>87,35; 91,87</t>
+          <t>87,45; 92,08</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>69,78; 76,16</t>
+          <t>69,63; 76,07</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>25,08; 33,2</t>
+          <t>25,46; 33,2</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>65,3; 71,81</t>
+          <t>65,58; 72,18</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>85,42; 89,91</t>
+          <t>85,3; 90,09</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>72,78; 78,78</t>
+          <t>72,74; 78,6</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>29,57; 36,88</t>
+          <t>29,85; 36,75</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>67,07; 71,51</t>
+          <t>67,03; 71,83</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>87,28; 90,51</t>
+          <t>87,12; 90,35</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>72,2; 76,7</t>
+          <t>72,33; 76,42</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>28,78; 33,89</t>
+          <t>28,77; 34,44</t>
         </is>
       </c>
     </row>
@@ -1920,4 +1921,2040 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N31"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Entrevistados que realiza cuidados a personas del hogar que lo requieren (tasa de respuesta: 100,0%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="n"/>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="n"/>
+      <c r="M1" s="3" t="n"/>
+      <c r="N1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+      <c r="L3" s="2" t="n"/>
+      <c r="M3" s="2" t="n"/>
+      <c r="N3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Almería</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>126</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>92</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>106</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>39802</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>24318</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>31874</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>13152</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>43289</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>37413</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>39063</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>6656</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>83091</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>61732</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>70938</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>19807</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>34804; 43321</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>22042; 25357</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>26808; 36370</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>5686; 31526</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>37776; 46871</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>34275; 38080</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>33194; 43632</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>3174; 11772</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>76386; 87847</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>58899; 62925</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>63431; 77081</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>11288; 39478</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Cádiz</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>105</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>149</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>153</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>37567</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>47522</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>46554</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>17866</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>31942</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>53163</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>54471</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>25271</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>69509</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>100685</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>101024</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>43137</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>30654; 43882</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>42150; 50512</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>39409; 52678</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>7967; 26883</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>25557; 38378</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>48948; 55823</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>47754; 61215</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>17435; 35498</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>60337; 78719</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>93941; 105170</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>91903; 110080</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>29643; 56482</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Córdoba</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>146</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>142</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>106</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>45919</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>48399</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>37498</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>9599</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>51931</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>53207</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>39283</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>9849</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>97851</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>101606</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>76780</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>19448</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>39333; 51452</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>43657; 51187</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>30598; 43026</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>5816; 14925</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>46323; 56772</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>48361; 56589</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>32860; 45809</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>6245; 14439</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>89352; 105936</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>95321; 106070</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>67300; 85077</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>14383; 26771</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Granada</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>165</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>122</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>52653</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>42634</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>25083</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>20572</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>58750</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>44386</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>37269</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>35817</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>111402</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>87020</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>62352</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>56390</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>47203; 57671</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>37496; 46144</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>19588; 30576</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>14446; 27891</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>53307; 64033</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>38488; 48779</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>31654; 41478</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>24377; 53178</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>103480; 118353</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>79481; 92923</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>53760; 69170</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>43147; 76809</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Huelva</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>96</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>7402</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>16381</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>30224</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>8552</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>5578</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>20472</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>34284</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>13601</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>12980</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>36853</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>64507</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>22153</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>4623; 8834</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>12919; 18043</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>25923; 31797</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>5281; 12628</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>2755; 8383</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>16432; 22662</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>31720; 35516</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>8803; 19078</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>9148; 16011</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>32225; 39853</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>60019; 66612</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>16425; 28431</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>Jaén</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>102</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>118</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n"/>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>31685</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>40780</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>17129</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>14471</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>35785</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>43312</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>23433</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>23259</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>67470</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>84092</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>40561</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>37730</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>26219; 36493</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>36445; 43062</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>12435; 20735</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>10194; 19574</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>29652; 40388</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>38057; 46242</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>18505; 26809</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>17989; 29715</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>59675; 74331</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>78519; 88128</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>34126; 45858</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>30727; 45980</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Málaga</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>127</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>151</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>116</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>154</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>118</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>237</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>305</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>234</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>87336</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>108240</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>74837</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>7916</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>76291</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>108250</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>79709</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>9807</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>163628</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>216489</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>154546</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>17723</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n"/>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>79083; 93141</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>102438; 111932</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>66584; 83018</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>4408; 13660</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>67328; 83832</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>102156; 113150</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>71300; 87314</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>4996; 17622</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>153324; 173876</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>207917; 222989</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>141759; 165704</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>11226; 26066</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>Sevilla</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>149</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>192</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>157</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>165</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>188</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>171</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>165</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>314</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>380</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>328</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="n"/>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>48365</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>100664</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>120444</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>105665</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>60256</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>113441</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>124338</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>126784</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>108622</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>214105</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>244782</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>232449</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="n"/>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>40745; 56241</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>94566; 105949</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>114651; 124197</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>97263; 113662</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>52451; 68210</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>106262; 119042</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>117571; 129914</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>116013; 134562</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr">
+        <is>
+          <t>96657; 118049</t>
+        </is>
+      </c>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>205248; 222017</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t>237148; 251892</t>
+        </is>
+      </c>
+      <c r="N27" s="2" t="inlineStr">
+        <is>
+          <t>219904; 243802</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>520</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>617</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>589</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>295</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>545</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>675</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>632</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>341</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>1065</t>
+        </is>
+      </c>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>1292</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>1221</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>636</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="n"/>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>350731</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>428939</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>383642</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>197792</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>363821</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>473645</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>431850</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>251045</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>714551</t>
+        </is>
+      </c>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>902584</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>815492</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>448837</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="n"/>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>333400; 366650</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>417091; 439171</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>365828; 399645</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>169597; 221165</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>346609; 381488</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>459598; 485395</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>415346; 448830</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>227448; 279996</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>691673; 741191</t>
+        </is>
+      </c>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>884960; 917749</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>792992; 837837</t>
+        </is>
+      </c>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t>410914; 491807</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="13">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A25:A27"/>
+    <mergeCell ref="A28:A30"/>
+    <mergeCell ref="A19:A21"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/P2C_R-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P2C_R-Provincia-trans_dic.xlsx
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>72,95; 90,81</t>
+          <t>74,33; 90,57</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>86,93; 100,0</t>
+          <t>85,82; 100,0</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>59,07; 80,13</t>
+          <t>58,78; 80,3</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>7,76; 43,02</t>
+          <t>7,5; 37,03</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>73,83; 91,61</t>
+          <t>75,48; 91,94</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>90,01; 100,0</t>
+          <t>88,65; 100,0</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>63,84; 83,92</t>
+          <t>64,54; 84,37</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>4,0; 14,83</t>
+          <t>4,39; 15,01</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>77,26; 88,85</t>
+          <t>77,62; 89,65</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>92,85; 99,19</t>
+          <t>92,47; 99,2</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>65,14; 79,16</t>
+          <t>64,91; 79,77</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>7,4; 25,86</t>
+          <t>7,48; 25,5</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>45,16; 64,64</t>
+          <t>45,16; 64,95</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>77,5; 92,88</t>
+          <t>78,01; 93,57</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>55,74; 74,51</t>
+          <t>56,47; 74,37</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6,24; 21,06</t>
+          <t>6,18; 21,55</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>39,36; 59,1</t>
+          <t>38,88; 58,45</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>83,12; 94,8</t>
+          <t>82,83; 95,63</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>59,7; 76,52</t>
+          <t>59,31; 75,96</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>13,66; 27,82</t>
+          <t>13,92; 27,07</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>45,43; 59,27</t>
+          <t>46,11; 59,31</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>82,93; 92,85</t>
+          <t>83,65; 93,28</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>60,98; 73,05</t>
+          <t>60,27; 73,27</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>11,61; 22,13</t>
+          <t>11,37; 21,85</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>60,8; 79,53</t>
+          <t>59,85; 80,41</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>82,82; 97,11</t>
+          <t>84,05; 96,31</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>52,65; 74,04</t>
+          <t>53,34; 75,29</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>9,98; 25,61</t>
+          <t>10,1; 25,0</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>68,22; 83,61</t>
+          <t>67,89; 83,61</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>80,69; 94,42</t>
+          <t>79,81; 94,3</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>49,65; 69,22</t>
+          <t>49,0; 69,64</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>9,3; 21,5</t>
+          <t>9,11; 23,41</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>67,38; 79,89</t>
+          <t>66,79; 80,06</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>84,62; 94,16</t>
+          <t>84,65; 93,97</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>54,15; 68,45</t>
+          <t>54,29; 68,97</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>11,47; 21,34</t>
+          <t>10,74; 20,67</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>71,46; 87,31</t>
+          <t>71,24; 86,17</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>75,48; 92,88</t>
+          <t>74,99; 92,75</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>43,42; 67,78</t>
+          <t>41,25; 67,33</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>20,59; 39,76</t>
+          <t>20,55; 40,59</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>72,51; 87,1</t>
+          <t>71,43; 86,45</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>69,38; 87,94</t>
+          <t>68,84; 88,35</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>66,43; 87,05</t>
+          <t>66,99; 86,99</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>31,2; 68,06</t>
+          <t>31,53; 67,32</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>74,14; 84,8</t>
+          <t>73,06; 84,61</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>75,59; 88,37</t>
+          <t>75,5; 88,35</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>57,95; 74,57</t>
+          <t>58,65; 75,26</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>29,1; 51,8</t>
+          <t>28,89; 51,79</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>48,45; 92,59</t>
+          <t>48,66; 92,6</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>71,6; 100,0</t>
+          <t>68,5; 100,0</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>80,07; 98,22</t>
+          <t>81,61; 98,24</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>15,3; 36,59</t>
+          <t>15,48; 37,13</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>24,17; 73,54</t>
+          <t>24,37; 72,86</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>66,72; 92,01</t>
+          <t>67,4; 91,98</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>89,31; 100,0</t>
+          <t>89,36; 100,0</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>21,62; 46,85</t>
+          <t>21,97; 47,17</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>43,68; 76,46</t>
+          <t>44,55; 78,38</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>75,52; 93,39</t>
+          <t>75,48; 93,84</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>88,41; 98,12</t>
+          <t>89,45; 98,28</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>21,83; 37,79</t>
+          <t>21,28; 38,19</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>56,19; 78,21</t>
+          <t>56,42; 78,55</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>81,82; 96,68</t>
+          <t>81,84; 96,64</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>45,58; 76,0</t>
+          <t>48,31; 78,28</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>22,08; 42,4</t>
+          <t>21,32; 41,94</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>56,73; 77,27</t>
+          <t>58,75; 79,46</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>76,83; 93,36</t>
+          <t>77,93; 93,49</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>59,02; 85,5</t>
+          <t>59,17; 86,92</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>32,02; 52,89</t>
+          <t>31,34; 51,03</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>60,32; 75,14</t>
+          <t>60,17; 75,44</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>83,46; 93,68</t>
+          <t>83,13; 93,63</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>58,2; 78,2</t>
+          <t>57,87; 78,69</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>30,02; 44,92</t>
+          <t>30,06; 44,48</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>71,47; 84,18</t>
+          <t>71,39; 85,3</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>87,78; 95,91</t>
+          <t>88,16; 96,34</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>57,02; 71,1</t>
+          <t>56,64; 71,05</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3,54; 10,97</t>
+          <t>3,3; 10,77</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>60,77; 75,67</t>
+          <t>61,87; 74,97</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>83,89; 92,92</t>
+          <t>83,85; 93,06</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>59,85; 73,3</t>
+          <t>58,75; 73,63</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>3,2; 11,3</t>
+          <t>3,49; 11,69</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>69,24; 78,52</t>
+          <t>69,05; 78,31</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>87,18; 93,5</t>
+          <t>87,72; 93,65</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>60,1; 70,25</t>
+          <t>60,2; 70,47</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>4,0; 9,29</t>
+          <t>4,15; 9,4</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>45,19; 62,37</t>
+          <t>44,15; 62,04</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>81,85; 91,7</t>
+          <t>81,56; 91,58</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>88,43; 95,79</t>
+          <t>88,28; 95,81</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>73,9; 86,36</t>
+          <t>73,56; 86,35</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>54,31; 70,63</t>
+          <t>54,09; 69,59</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>81,45; 91,24</t>
+          <t>81,18; 91,35</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>84,45; 93,31</t>
+          <t>84,31; 92,84</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>73,99; 85,82</t>
+          <t>74,43; 86,27</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>51,76; 63,21</t>
+          <t>52,31; 64,18</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>83,43; 90,25</t>
+          <t>83,17; 90,4</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>88,2; 93,68</t>
+          <t>88,09; 93,73</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>76,25; 84,53</t>
+          <t>76,2; 84,58</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>66,23; 72,84</t>
+          <t>66,48; 72,97</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>87,45; 92,08</t>
+          <t>87,71; 91,95</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>69,63; 76,07</t>
+          <t>69,96; 76,33</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>25,46; 33,2</t>
+          <t>25,47; 33,17</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>65,58; 72,18</t>
+          <t>65,6; 72,01</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>85,3; 90,09</t>
+          <t>85,66; 90,27</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>72,74; 78,6</t>
+          <t>72,45; 78,47</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>29,85; 36,75</t>
+          <t>29,46; 37,15</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>67,03; 71,83</t>
+          <t>66,82; 71,58</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>87,12; 90,35</t>
+          <t>87,09; 90,42</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>72,33; 76,42</t>
+          <t>72,17; 76,44</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>28,77; 34,44</t>
+          <t>28,7; 33,82</t>
         </is>
       </c>
     </row>
@@ -2209,62 +2209,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>34804; 43321</t>
+          <t>35461; 43207</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>22042; 25357</t>
+          <t>21762; 25357</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>26808; 36370</t>
+          <t>26677; 36447</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>5686; 31526</t>
+          <t>5494; 27138</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>37776; 46871</t>
+          <t>38621; 47043</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>34275; 38080</t>
+          <t>33760; 38080</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>33194; 43632</t>
+          <t>33558; 43867</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>3174; 11772</t>
+          <t>3485; 11913</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>76386; 87847</t>
+          <t>76746; 88635</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>58899; 62925</t>
+          <t>58663; 62931</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>63431; 77081</t>
+          <t>63209; 77680</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>11288; 39478</t>
+          <t>11414; 38927</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>30654; 43882</t>
+          <t>30655; 44092</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>42150; 50512</t>
+          <t>42428; 50889</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>39409; 52678</t>
+          <t>39926; 52582</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>7967; 26883</t>
+          <t>7894; 27506</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>25557; 38378</t>
+          <t>25246; 37952</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>48948; 55823</t>
+          <t>48776; 56315</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>47754; 61215</t>
+          <t>47447; 60764</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>17435; 35498</t>
+          <t>17765; 34542</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>60337; 78719</t>
+          <t>61237; 78776</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>93941; 105170</t>
+          <t>94756; 105663</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>91903; 110080</t>
+          <t>90828; 110420</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>29643; 56482</t>
+          <t>29013; 55763</t>
         </is>
       </c>
     </row>
@@ -2625,62 +2625,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>39333; 51452</t>
+          <t>38718; 52020</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>43657; 51187</t>
+          <t>44305; 50768</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>30598; 43026</t>
+          <t>30997; 43753</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>5816; 14925</t>
+          <t>5887; 14569</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>46323; 56772</t>
+          <t>46099; 56776</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>48361; 56589</t>
+          <t>47831; 56520</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>32860; 45809</t>
+          <t>32424; 46088</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>6245; 14439</t>
+          <t>6121; 15726</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>89352; 105936</t>
+          <t>88566; 106161</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>95321; 106070</t>
+          <t>95361; 105859</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>67300; 85077</t>
+          <t>67479; 85724</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>14383; 26771</t>
+          <t>13471; 25931</t>
         </is>
       </c>
     </row>
@@ -2833,62 +2833,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>47203; 57671</t>
+          <t>47059; 56921</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>37496; 46144</t>
+          <t>37256; 46076</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>19588; 30576</t>
+          <t>18608; 30375</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>14446; 27891</t>
+          <t>14413; 28470</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>53307; 64033</t>
+          <t>52515; 63556</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>38488; 48779</t>
+          <t>38187; 49007</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>31654; 41478</t>
+          <t>31919; 41451</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>24377; 53178</t>
+          <t>24635; 52603</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>103480; 118353</t>
+          <t>101965; 118085</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>79481; 92923</t>
+          <t>79386; 92904</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>53760; 69170</t>
+          <t>54402; 69818</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>43147; 76809</t>
+          <t>42841; 76791</t>
         </is>
       </c>
     </row>
@@ -3041,62 +3041,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>4623; 8834</t>
+          <t>4643; 8835</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>12919; 18043</t>
+          <t>12360; 18043</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>25923; 31797</t>
+          <t>26420; 31804</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>5281; 12628</t>
+          <t>5342; 12814</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>2755; 8383</t>
+          <t>2778; 8305</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>16432; 22662</t>
+          <t>16601; 22655</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>31720; 35516</t>
+          <t>31737; 35516</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>8803; 19078</t>
+          <t>8946; 19206</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>9148; 16011</t>
+          <t>9329; 16413</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>32225; 39853</t>
+          <t>32209; 40043</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>60019; 66612</t>
+          <t>60731; 66721</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>16425; 28431</t>
+          <t>16008; 28728</t>
         </is>
       </c>
     </row>
@@ -3249,62 +3249,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>26219; 36493</t>
+          <t>26326; 36649</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>36445; 43062</t>
+          <t>36451; 43045</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>12435; 20735</t>
+          <t>13180; 21357</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>10194; 19574</t>
+          <t>9845; 19365</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>29652; 40388</t>
+          <t>30708; 41534</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>38057; 46242</t>
+          <t>38600; 46310</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>18505; 26809</t>
+          <t>18553; 27254</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>17989; 29715</t>
+          <t>17611; 28671</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>59675; 74331</t>
+          <t>59528; 74630</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>78519; 88128</t>
+          <t>78203; 88081</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>34126; 45858</t>
+          <t>33936; 46140</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>30727; 45980</t>
+          <t>30768; 45524</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>79083; 93141</t>
+          <t>78993; 94377</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>102438; 111932</t>
+          <t>102888; 112436</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>66584; 83018</t>
+          <t>66140; 82964</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>4408; 13660</t>
+          <t>4106; 13410</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>67328; 83832</t>
+          <t>68541; 83055</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>102156; 113150</t>
+          <t>102108; 113331</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>71300; 87314</t>
+          <t>69982; 87712</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>4996; 17622</t>
+          <t>5439; 18243</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>153324; 173876</t>
+          <t>152910; 173395</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>207917; 222989</t>
+          <t>209198; 223327</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>141759; 165704</t>
+          <t>142006; 166242</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>11226; 26066</t>
+          <t>11650; 26371</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>40745; 56241</t>
+          <t>39810; 55942</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>94566; 105949</t>
+          <t>94239; 105812</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>114651; 124197</t>
+          <t>114461; 124220</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>97263; 113662</t>
+          <t>96820; 113659</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>52451; 68210</t>
+          <t>52241; 67206</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>106262; 119042</t>
+          <t>105915; 119183</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>117571; 129914</t>
+          <t>117380; 129255</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>116013; 134562</t>
+          <t>116710; 135272</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>96657; 118049</t>
+          <t>97683; 119857</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>205248; 222017</t>
+          <t>204596; 222395</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>237148; 251892</t>
+          <t>236860; 252016</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>219904; 243802</t>
+          <t>219767; 243951</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>333400; 366650</t>
+          <t>334656; 367316</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>417091; 439171</t>
+          <t>418324; 438557</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>365828; 399645</t>
+          <t>367557; 401043</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>169597; 221165</t>
+          <t>169639; 220990</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>346609; 381488</t>
+          <t>346730; 380608</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>459598; 485395</t>
+          <t>461494; 486339</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>415346; 448830</t>
+          <t>413730; 448105</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>227448; 279996</t>
+          <t>224471; 283042</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>691673; 741191</t>
+          <t>689538; 738597</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>884960; 917749</t>
+          <t>884572; 918467</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>792992; 837837</t>
+          <t>791295; 838073</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>410914; 491807</t>
+          <t>409924; 482981</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P2C_R-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P2C_R-Provincia-trans_dic.xlsx
@@ -533,7 +533,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -541,7 +541,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -649,42 +649,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>84,61%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>98,25%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>75,13%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>8,68%</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>83,43%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>95,9%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>70,23%</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>17,95%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>84,61%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>98,25%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>75,13%</t>
-        </is>
-      </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>8,39%</t>
+          <t>10,69%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>12,98%</t>
+          <t>9,62%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>74,33; 90,57</t>
+          <t>74,65; 91,35</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>85,82; 100,0</t>
+          <t>91,14; 100,0</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>58,78; 80,3</t>
+          <t>63,32; 83,73</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>7,5; 37,03</t>
+          <t>4,11; 14,89</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>75,48; 91,94</t>
+          <t>72,86; 90,41</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>88,65; 100,0</t>
+          <t>86,39; 100,0</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>64,54; 84,37</t>
+          <t>59,39; 81,54</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>4,39; 15,01</t>
+          <t>5,52; 18,54</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>77,62; 89,65</t>
+          <t>77,2; 89,75</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>92,47; 99,2</t>
+          <t>92,83; 99,23</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>64,91; 79,77</t>
+          <t>64,11; 79,19</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>7,48; 25,5</t>
+          <t>5,84; 14,21</t>
         </is>
       </c>
     </row>
@@ -789,42 +789,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>49,19%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>90,28%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>68,09%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>19,26%</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>55,34%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>87,38%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>65,85%</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>14,0%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>49,19%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>90,28%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>68,09%</t>
-        </is>
-      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>19,81%</t>
+          <t>17,25%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>16,9%</t>
+          <t>18,32%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>45,16; 64,95</t>
+          <t>39,25; 59,21</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>78,01; 93,57</t>
+          <t>81,6; 94,74</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>56,47; 74,37</t>
+          <t>59,28; 75,69</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6,18; 21,55</t>
+          <t>13,31; 26,85</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>38,88; 58,45</t>
+          <t>45,81; 64,68</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>82,83; 95,63</t>
+          <t>78,82; 93,05</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>59,31; 75,96</t>
+          <t>56,15; 74,69</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>13,92; 27,07</t>
+          <t>11,87; 24,26</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>46,11; 59,31</t>
+          <t>44,97; 59,9</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>83,65; 93,28</t>
+          <t>82,97; 92,7</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>60,27; 73,27</t>
+          <t>60,43; 72,62</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>11,37; 21,85</t>
+          <t>14,05; 23,52</t>
         </is>
       </c>
     </row>
@@ -929,42 +929,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>76,48%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>88,78%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>59,36%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>14,27%</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>70,98%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>91,82%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>64,53%</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>16,47%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>76,48%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>88,78%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>59,36%</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>14,66%</t>
+          <t>16,53%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>15,5%</t>
+          <t>15,37%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>59,85; 80,41</t>
+          <t>67,6; 83,86</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>84,05; 96,31</t>
+          <t>80,67; 94,35</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>53,34; 75,29</t>
+          <t>49,56; 69,56</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>10,1; 25,0</t>
+          <t>8,16; 22,1</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>67,89; 83,61</t>
+          <t>60,95; 79,22</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>79,81; 94,3</t>
+          <t>83,24; 97,28</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>49,0; 69,64</t>
+          <t>52,89; 74,86</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>9,11; 23,41</t>
+          <t>10,2; 24,78</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>66,79; 80,06</t>
+          <t>66,65; 79,63</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>84,65; 93,97</t>
+          <t>84,52; 94,43</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>54,29; 68,97</t>
+          <t>54,2; 68,59</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>10,74; 20,67</t>
+          <t>10,5; 20,56</t>
         </is>
       </c>
     </row>
@@ -1069,42 +1069,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>79,91%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>80,02%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>78,21%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>44,46%</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>79,71%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>85,82%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>55,6%</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>29,33%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>79,91%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>80,02%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>78,21%</t>
-        </is>
-      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>45,84%</t>
+          <t>29,03%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>38,03%</t>
+          <t>36,82%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>71,24; 86,17</t>
+          <t>71,14; 86,75</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>74,99; 92,75</t>
+          <t>67,77; 88,29</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>41,25; 67,33</t>
+          <t>67,17; 87,26</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>20,55; 40,59</t>
+          <t>30,89; 66,1</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>71,43; 86,45</t>
+          <t>70,94; 87,36</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>68,84; 88,35</t>
+          <t>75,57; 92,49</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>66,99; 86,99</t>
+          <t>42,9; 67,27</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>31,53; 67,32</t>
+          <t>20,94; 40,29</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>73,06; 84,61</t>
+          <t>73,98; 84,96</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>75,5; 88,35</t>
+          <t>75,98; 88,6</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>58,65; 75,26</t>
+          <t>59,0; 74,86</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>28,89; 51,79</t>
+          <t>28,95; 50,16</t>
         </is>
       </c>
     </row>
@@ -1209,42 +1209,42 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>48,93%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>83,12%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>96,53%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>31,31%</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
           <t>77,58%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>90,79%</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>93,36%</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>24,78%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>48,93%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>83,12%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>96,53%</t>
-        </is>
-      </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>33,4%</t>
+          <t>25,44%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>29,45%</t>
+          <t>28,53%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>48,66; 92,6</t>
+          <t>24,53; 74,88</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>68,5; 100,0</t>
+          <t>68,03; 93,86</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>81,61; 98,24</t>
+          <t>89,14; 100,0</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>15,48; 37,13</t>
+          <t>21,52; 46,18</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>24,37; 72,86</t>
+          <t>48,75; 92,62</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>67,4; 91,98</t>
+          <t>71,53; 100,0</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>89,36; 100,0</t>
+          <t>83,09; 98,23</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>21,97; 47,17</t>
+          <t>15,54; 37,85</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>44,55; 78,38</t>
+          <t>42,28; 79,39</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>75,48; 93,84</t>
+          <t>74,94; 93,54</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>89,45; 98,28</t>
+          <t>89,33; 98,2</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>21,28; 38,19</t>
+          <t>20,66; 36,21</t>
         </is>
       </c>
     </row>
@@ -1349,42 +1349,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>68,46%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>87,44%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>74,73%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>39,77%</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>67,91%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>91,55%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>62,78%</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>31,35%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>68,46%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>87,44%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>74,73%</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>41,4%</t>
+          <t>28,85%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>36,86%</t>
+          <t>34,49%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>56,42; 78,55</t>
+          <t>56,12; 77,92</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>81,84; 96,64</t>
+          <t>78,57; 93,94</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>48,31; 78,28</t>
+          <t>59,01; 86,45</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>21,32; 41,94</t>
+          <t>29,96; 49,65</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>58,75; 79,46</t>
+          <t>55,96; 77,46</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>77,93; 93,49</t>
+          <t>80,78; 96,64</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>59,17; 86,92</t>
+          <t>46,22; 78,52</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>31,34; 51,03</t>
+          <t>19,93; 39,58</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>60,17; 75,44</t>
+          <t>60,14; 75,73</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>83,13; 93,63</t>
+          <t>82,97; 93,78</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>57,87; 78,69</t>
+          <t>59,53; 78,65</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>30,06; 44,48</t>
+          <t>27,09; 41,13</t>
         </is>
       </c>
     </row>
@@ -1489,42 +1489,42 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>68,86%</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>88,89%</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>66,91%</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>6,13%</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>78,93%</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>92,75%</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>64,09%</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>6,36%</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>68,86%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>88,89%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>66,91%</t>
-        </is>
-      </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>6,29%</t>
+          <t>6,54%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>71,39; 85,3</t>
+          <t>60,88; 75,22</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>88,16; 96,34</t>
+          <t>83,14; 93,0</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>56,64; 71,05</t>
+          <t>59,3; 73,47</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3,3; 10,77</t>
+          <t>3,4; 11,59</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>61,87; 74,97</t>
+          <t>72,57; 85,35</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>83,85; 93,06</t>
+          <t>88,29; 95,92</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>58,75; 73,63</t>
+          <t>56,66; 71,71</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>3,49; 11,69</t>
+          <t>3,58; 10,63</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>69,05; 78,31</t>
+          <t>68,4; 78,26</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>87,72; 93,65</t>
+          <t>87,39; 93,56</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>60,2; 70,47</t>
+          <t>59,78; 70,56</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>4,15; 9,4</t>
+          <t>3,97; 9,46</t>
         </is>
       </c>
     </row>
@@ -1629,42 +1629,42 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>62,39%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>86,95%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>89,31%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>80,54%</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
           <t>53,64%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="H18" s="2" t="inlineStr">
         <is>
           <t>87,13%</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="I18" s="2" t="inlineStr">
         <is>
           <t>92,9%</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>80,28%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>62,39%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>86,95%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>89,31%</t>
-        </is>
-      </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>80,86%</t>
+          <t>79,19%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>80,6%</t>
+          <t>79,91%</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>44,15; 62,04</t>
+          <t>54,86; 69,87</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>81,56; 91,58</t>
+          <t>80,93; 91,1</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>88,28; 95,81</t>
+          <t>84,24; 93,04</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>73,56; 86,35</t>
+          <t>74,36; 85,69</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>54,09; 69,59</t>
+          <t>44,26; 61,62</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>81,18; 91,35</t>
+          <t>82,06; 91,95</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>84,31; 92,84</t>
+          <t>88,47; 95,92</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>74,43; 86,27</t>
+          <t>71,4; 84,99</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>52,31; 64,18</t>
+          <t>52,01; 63,44</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>83,17; 90,4</t>
+          <t>83,38; 90,28</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>88,09; 93,73</t>
+          <t>88,16; 93,61</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>76,2; 84,58</t>
+          <t>74,94; 84,42</t>
         </is>
       </c>
     </row>
@@ -1769,42 +1769,42 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>68,83%</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>87,91%</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>75,63%</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>33,87%</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
           <t>69,68%</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>89,93%</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="I20" s="2" t="inlineStr">
         <is>
           <t>73,02%</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>29,69%</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>68,83%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>87,91%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>75,63%</t>
-        </is>
-      </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>32,95%</t>
+          <t>30,97%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1824,7 +1824,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>31,43%</t>
+          <t>32,49%</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>66,48; 72,97</t>
+          <t>65,3; 71,81</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>87,71; 91,95</t>
+          <t>85,42; 89,91</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>69,96; 76,33</t>
+          <t>72,78; 78,78</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>25,47; 33,17</t>
+          <t>30,61; 37,73</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>65,6; 72,01</t>
+          <t>66,16; 72,69</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>85,66; 90,27</t>
+          <t>87,35; 91,87</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>72,45; 78,47</t>
+          <t>69,78; 76,16</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>29,46; 37,15</t>
+          <t>28,03; 34,14</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>66,82; 71,58</t>
+          <t>67,07; 71,51</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>87,09; 90,42</t>
+          <t>87,28; 90,51</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>72,17; 76,44</t>
+          <t>72,2; 76,7</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>28,7; 33,82</t>
+          <t>30,14; 34,7</t>
         </is>
       </c>
     </row>
@@ -1957,7 +1957,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -1965,7 +1965,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -2073,37 +2073,37 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>65</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>51</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>61</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>52</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>55</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2141,42 +2141,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>43289</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>37413</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>39063</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>5566</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
           <t>39802</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>24318</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>31874</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>13152</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>43289</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>37413</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>39063</t>
-        </is>
-      </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>6656</t>
+          <t>6038</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>19807</t>
+          <t>11604</t>
         </is>
       </c>
     </row>
@@ -2209,62 +2209,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>35461; 43207</t>
+          <t>38193; 46739</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>21762; 25357</t>
+          <t>34706; 38080</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>26677; 36447</t>
+          <t>32920; 43535</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>5494; 27138</t>
+          <t>2634; 9552</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>38621; 47043</t>
+          <t>34761; 43133</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>33760; 38080</t>
+          <t>21907; 25357</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>33558; 43867</t>
+          <t>26957; 37007</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>3485; 11913</t>
+          <t>3116; 10470</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>76746; 88635</t>
+          <t>76327; 88741</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>58663; 62931</t>
+          <t>58889; 62950</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>63209; 77680</t>
+          <t>62432; 77111</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>11414; 38927</t>
+          <t>7048; 17138</t>
         </is>
       </c>
     </row>
@@ -2281,42 +2281,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
           <t>57</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>69</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>72</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>27</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>81</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>38</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -2349,42 +2349,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>31942</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>53163</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>54471</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>22315</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>37567</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>47522</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>46554</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>17866</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>31942</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>53163</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>54471</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>25271</t>
+          <t>17491</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2404,7 +2404,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>43137</t>
+          <t>39806</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>30655; 44092</t>
+          <t>25490; 38445</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>42428; 50889</t>
+          <t>48049; 55788</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>39926; 52582</t>
+          <t>47423; 60546</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>7894; 27506</t>
+          <t>15413; 31099</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>25246; 37952</t>
+          <t>31099; 43912</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>48776; 56315</t>
+          <t>42867; 50605</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>47447; 60764</t>
+          <t>39699; 52805</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>17765; 34542</t>
+          <t>12038; 24594</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>61237; 78776</t>
+          <t>59734; 79559</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>94756; 105663</t>
+          <t>93984; 105009</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>90828; 110420</t>
+          <t>91064; 109434</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>29013; 55763</t>
+          <t>30518; 51102</t>
         </is>
       </c>
     </row>
@@ -2489,42 +2489,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>63</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>66</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>50</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>17</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>83</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>76</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>56</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -2557,42 +2557,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>51931</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>53207</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>39283</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>8473</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
           <t>45919</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>48399</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>37498</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>9599</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>51931</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>53207</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>39283</t>
-        </is>
-      </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>9849</t>
+          <t>9347</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2612,7 +2612,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>19448</t>
+          <t>17820</t>
         </is>
       </c>
     </row>
@@ -2625,62 +2625,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>38718; 52020</t>
+          <t>45903; 56943</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>44305; 50768</t>
+          <t>48349; 56547</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>30997; 43753</t>
+          <t>32800; 46036</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>5887; 14569</t>
+          <t>4844; 13122</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>46099; 56776</t>
+          <t>39430; 51254</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>47831; 56520</t>
+          <t>43879; 51277</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>32424; 46088</t>
+          <t>30736; 43503</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>6121; 15726</t>
+          <t>5770; 14018</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>88566; 106161</t>
+          <t>88378; 105596</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>95361; 105859</t>
+          <t>95213; 106374</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>67479; 85724</t>
+          <t>67362; 85247</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>13471; 25931</t>
+          <t>12175; 23835</t>
         </is>
       </c>
     </row>
@@ -2697,42 +2697,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
           <t>79</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>62</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>36</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>29</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>86</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>27</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -2765,42 +2765,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>58750</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>44386</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>37269</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>32086</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>52653</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>42634</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>25083</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>20572</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>58750</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>44386</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>37269</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>35817</t>
+          <t>20564</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2820,7 +2820,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>56390</t>
+          <t>52650</t>
         </is>
       </c>
     </row>
@@ -2833,62 +2833,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>47059; 56921</t>
+          <t>52303; 63778</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>37256; 46076</t>
+          <t>37593; 48975</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>18608; 30375</t>
+          <t>32005; 41580</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>14413; 28470</t>
+          <t>22294; 47699</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>52515; 63556</t>
+          <t>46861; 57707</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>38187; 49007</t>
+          <t>37544; 45948</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>31919; 41451</t>
+          <t>19354; 30346</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>24635; 52603</t>
+          <t>14833; 28542</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>101965; 118085</t>
+          <t>103249; 118581</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>79386; 92904</t>
+          <t>79892; 93161</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>54402; 69818</t>
+          <t>54731; 69440</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>42841; 76791</t>
+          <t>41396; 71734</t>
         </is>
       </c>
     </row>
@@ -2905,42 +2905,42 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>45</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="J16" s="2" t="inlineStr">
         <is>
           <t>16</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -2973,42 +2973,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>5578</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>20472</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>34284</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>12394</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
           <t>7402</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>16381</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="I17" s="2" t="inlineStr">
         <is>
           <t>30224</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>8552</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>5578</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>20472</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>34284</t>
-        </is>
-      </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>13601</t>
+          <t>9059</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -3028,7 +3028,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>22153</t>
+          <t>21453</t>
         </is>
       </c>
     </row>
@@ -3041,62 +3041,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>4643; 8835</t>
+          <t>2796; 8535</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>12360; 18043</t>
+          <t>16757; 23117</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>26420; 31804</t>
+          <t>31657; 35516</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>5342; 12814</t>
+          <t>8517; 18277</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>2778; 8305</t>
+          <t>4651; 8837</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>16601; 22655</t>
+          <t>12906; 18043</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>31737; 35516</t>
+          <t>26900; 31803</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>8946; 19206</t>
+          <t>5532; 13477</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>9329; 16413</t>
+          <t>8854; 16625</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>32209; 40043</t>
+          <t>31979; 39918</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>60731; 66721</t>
+          <t>60644; 66671</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>16008; 28728</t>
+          <t>15537; 27224</t>
         </is>
       </c>
     </row>
@@ -3113,42 +3113,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
           <t>46</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="H19" s="2" t="inlineStr">
         <is>
           <t>58</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="I19" s="2" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="J19" s="2" t="inlineStr">
         <is>
           <t>27</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>56</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>45</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
@@ -3181,42 +3181,42 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>35785</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>43312</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>23433</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>19463</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
           <t>31685</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>40780</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="I20" s="2" t="inlineStr">
         <is>
           <t>17129</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>14471</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>35785</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>43312</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>23433</t>
-        </is>
-      </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>23259</t>
+          <t>13205</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>37730</t>
+          <t>32668</t>
         </is>
       </c>
     </row>
@@ -3249,62 +3249,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>26326; 36649</t>
+          <t>29333; 40731</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>36451; 43045</t>
+          <t>38919; 46534</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>13180; 21357</t>
+          <t>18504; 27108</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>9845; 19365</t>
+          <t>14662; 24302</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>30708; 41534</t>
+          <t>26111; 36143</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>38600; 46310</t>
+          <t>35980; 43044</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>18553; 27254</t>
+          <t>12609; 21422</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>17611; 28671</t>
+          <t>9119; 18113</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>59528; 74630</t>
+          <t>59498; 74915</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>78203; 88081</t>
+          <t>78057; 88224</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>33936; 46140</t>
+          <t>34908; 46121</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>30768; 45524</t>
+          <t>25657; 38956</t>
         </is>
       </c>
     </row>
@@ -3321,37 +3321,37 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>154</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>118</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
           <t>127</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="H22" s="2" t="inlineStr">
         <is>
           <t>151</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="I22" s="2" t="inlineStr">
         <is>
           <t>116</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>110</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>154</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>118</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -3389,42 +3389,42 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>76291</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>108250</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>79709</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>8665</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
           <t>87336</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="H23" s="2" t="inlineStr">
         <is>
           <t>108240</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="I23" s="2" t="inlineStr">
         <is>
           <t>74837</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>7916</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>76291</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>108250</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>79709</t>
-        </is>
-      </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>9807</t>
+          <t>8013</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3444,7 +3444,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>17723</t>
+          <t>16678</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>78993; 94377</t>
+          <t>67447; 83335</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>102888; 112436</t>
+          <t>101243; 113251</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>66140; 82964</t>
+          <t>70643; 87519</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>4106; 13410</t>
+          <t>4804; 16383</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>68541; 83055</t>
+          <t>80294; 94433</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>102108; 113331</t>
+          <t>103040; 111947</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>69982; 87712</t>
+          <t>66164; 83732</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>5439; 18243</t>
+          <t>4383; 13021</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>152910; 173395</t>
+          <t>151465; 173300</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>209198; 223327</t>
+          <t>208404; 223128</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>142006; 166242</t>
+          <t>141021; 166431</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>11650; 26371</t>
+          <t>10465; 24955</t>
         </is>
       </c>
     </row>
@@ -3529,42 +3529,42 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>165</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>188</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>171</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
           <t>72</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="H25" s="2" t="inlineStr">
         <is>
           <t>149</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
+      <c r="I25" s="2" t="inlineStr">
         <is>
           <t>192</t>
         </is>
       </c>
-      <c r="F25" s="2" t="inlineStr">
+      <c r="J25" s="2" t="inlineStr">
         <is>
           <t>157</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>93</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>165</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>188</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>171</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
@@ -3597,42 +3597,42 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>60256</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>113441</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>124338</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>128406</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
           <t>48365</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="H26" s="2" t="inlineStr">
         <is>
           <t>100664</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="I26" s="2" t="inlineStr">
         <is>
           <t>120444</t>
         </is>
       </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>105665</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>60256</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>113441</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>124338</t>
-        </is>
-      </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>126784</t>
+          <t>111265</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3652,7 +3652,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>232449</t>
+          <t>239670</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>39810; 55942</t>
+          <t>52981; 67482</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>94239; 105812</t>
+          <t>105592; 118851</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>114461; 124220</t>
+          <t>117285; 129537</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>96820; 113659</t>
+          <t>118550; 136611</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>52241; 67206</t>
+          <t>39912; 55558</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>105915; 119183</t>
+          <t>94814; 106239</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>117380; 129255</t>
+          <t>114701; 124361</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>116710; 135272</t>
+          <t>100313; 119405</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>97683; 119857</t>
+          <t>97120; 118478</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>204596; 222395</t>
+          <t>205112; 222084</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>236860; 252016</t>
+          <t>237037; 251701</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>219767; 243951</t>
+          <t>224762; 253198</t>
         </is>
       </c>
     </row>
@@ -3737,42 +3737,42 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>545</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>675</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>632</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>341</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
           <t>520</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="H28" s="2" t="inlineStr">
         <is>
           <t>617</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
+      <c r="I28" s="2" t="inlineStr">
         <is>
           <t>589</t>
         </is>
       </c>
-      <c r="F28" s="2" t="inlineStr">
+      <c r="J28" s="2" t="inlineStr">
         <is>
           <t>295</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>545</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>675</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>632</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>341</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
@@ -3805,42 +3805,42 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
+          <t>363821</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>473645</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>431850</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>237366</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
           <t>350731</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="H29" s="2" t="inlineStr">
         <is>
           <t>428939</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
+      <c r="I29" s="2" t="inlineStr">
         <is>
           <t>383642</t>
         </is>
       </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>197792</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>363821</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>473645</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>431850</t>
-        </is>
-      </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>251045</t>
+          <t>194981</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -3860,7 +3860,7 @@
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>448837</t>
+          <t>432348</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>334656; 367316</t>
+          <t>345138; 379567</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>418324; 438557</t>
+          <t>460235; 484394</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>367557; 401043</t>
+          <t>415584; 449887</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>169639; 220990</t>
+          <t>214504; 264437</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>346730; 380608</t>
+          <t>333008; 365889</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>461494; 486339</t>
+          <t>416621; 438190</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>413730; 448105</t>
+          <t>366597; 400140</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>224471; 283042</t>
+          <t>176518; 214951</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>689538; 738597</t>
+          <t>692115; 737936</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>884572; 918467</t>
+          <t>886523; 919393</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>791295; 838073</t>
+          <t>791620; 840951</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>409924; 482981</t>
+          <t>400997; 461688</t>
         </is>
       </c>
     </row>
